--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnNoticeExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnNoticeExport.xlsx
@@ -91,7 +91,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.returnTypeDict}</t>
+    <t>{.returnTypeDictName}</t>
   </si>
   <si>
     <t>{.salesQty}</t>
